--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,12 +498,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OYO</t>
+          <t>Miftah</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ritesh Agarwal</t>
+          <t>Miftah Mizwar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,17 +513,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/in/riteshagar</t>
+          <t>https://id.linkedin.com/in/miftahmizwar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.oyolasvegas.com/</t>
+          <t>https://miftah.in</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ritesh.agarwal@oyolasvegas.com</t>
+          <t>miftah.mizwar@miftah.in</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -531,42 +531,42 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Congratulations on Sunday Proptech Fundraise</t>
+          <t>Congrats on the pre-seed round</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hi Ritesh, I saw the news about OYO's ₹200 Crore fundraise and wanted to reach out. This is a significant milestone, and I'm excited to see the impact it will have on the company's growth. I'm interested in learning more about your plans for this investment and how it might align with our services. Perhaps we could discuss this further in a quick 15-minute chat? Best regards, Imran</t>
+          <t>Miftah, I saw the news about Miftah's pre-seed round and wanted to reach out. This is an exciting time for your company, and I'd love to explore how we can support your growth. Can we schedule a 15-minute call to discuss further?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQeTczZzRXRVE5UTAyblZwRWhUM29BSXJmUXhzVVAyeHBXcTZUMm1SX1NldEphOEpvWEZMMUlTT3VYNGNaQ2RvU25sdHhvNmNBUHl5MmVvZU1BSmZqWWFnczUxV3lNQzFVMGhoRUtZYkNqcHVDcGZQcldRUWxMTHYyb2RNMTl6QkVWUU56MU90VWJFZjl5M1JhQ2cyOURmWG8xOVR3dWRaQmdyTzA5MmNSdXhOVlJjeDlCLUFDRlVFODhaYmV0Y1MxUTAxNVJRU00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE0tcTVkUlJDVDZ2dzlvc1VUMHFEZ2F6OHNUcmNMQU81WVRlTTh3ZjJQRjJ6N1BlWWllTjFlSG9DaG1rYWpXOXdvNk43djRZZnZwYlVpck9FMVFUenF1bVZaVWsxek80RUhrbG5aTnc3b3NqWmw1MUIxdC1XZnJvUVE?oc=5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sunday Proptech (OYO) ₹200 Crore Fundraise</t>
+          <t>Syrian proptech Miftah raises pre-seed round</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OfficeBanao</t>
+          <t>OYO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Akhilesh Agarwal</t>
+          <t>Ritesh Aggarwal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -576,17 +576,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/in/akhileshagarwalcfo</t>
+          <t>https://in.linkedin.com/in/ritesh-aggarwal-585b97356</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://officebanao.com/</t>
+          <t>https://oyo.io</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>akhilesh.agarwal@officebanao.com</t>
+          <t>ritesh.aggarwal@oyo.io</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -594,22 +594,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Congratulations on OfficeBanao's Funding</t>
+          <t>Congratulations on the Funding</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hi Akhilesh, I came across the news about OfficeBanao raising $4 million in funding and wanted to reach out. This is a significant milestone, and I'm excited to see the impact it will have on your business. As someone who's been following the proptech space, I'm curious to learn more about your plans for growth. I'd love to explore potential synergies and see if there's anything I can help with. Would you be open to a quick 15-minute chat? Best regards, Imran</t>
+          <t>Ritesh, I saw the news about Sunday Proptech raising ₹200 Crore in funding and wanted to reach out. This investment will likely bring new opportunities and challenges for OYO. I'd love to discuss how we can help support your growth. Can we schedule a 15-minute call?</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOTXRWZllNSl90YmgxYjVMV0UyRFg0dTg0UmRvUFRkRzRHdnUyRHpUdDhYSkdoUGpuVU9kZExsaWxlTmZjenVJZV83SWs4ZjZJdVJzWi11dVlSWVpkRW1jM2luV1F2MXQtbFM0ZWY4UDdLcUR6VWh2YXhsRi11bFZ1bS0xME5teWxjSTlxZllBcU9FaHZzSHBLVEVwS0hMZ05tWHNRMmw5WDJmMEJTV2ZIVjBXdmZaSk8zdW1fSVgtU2E2MTlYbjJueUN1RjFYNHRfZVA5VjdUa0_SAdgBQVVfeXFMTk10VmZZTUpfdGJoMWI1TFdFMkRYNHU4NFJkb1BUZEc0R3Z1MkR6VHQ4WEpHaFBqblVPZGRMbGlsZU5mY3p1SWVfN0lrOGY2SXVSc1otdXVZUllaZEVtYzNpbldRdjF0LWxTNGVmOFA3S3FEelVodmF4bEYtdWxWdW0tMTBObXlsY0k5cWZZQXFPRWh2c0hwS1RFcEtITGdObVhzUTJsOVgyZjBCU1dmSFYwV3ZmWkpPM3VtX0lYLVNhNjE5WG4ybnlDdUYxWDR0X2VQOVY3VGtP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQeTczZzRXRVE5UTAyblZwRWhUM29BSXJmUXhzVVAyeHBXcTZUMm1SX1NldEphOEpvWEZMMUlTT3VYNGNaQ2RvU25sdHhvNmNBUHl5MmVvZU1BSmZqWWFnczUxV3lNQzFVMGhoRUtZYkNqcHVDcGZQcldRUWxMTHYyb2RNMTl6QkVWUU56MU90VWJFZjl5M1JhQ2cyOURmWG8xOVR3dWRaQmdyTzA5MmNSdXhOVlJjeDlCLUFDRlVFODhaYmV0Y1MxUTAxNVJRU00?oc=5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Gurugram's proptech startup OfficeBanao raises $4 million in funding</t>
+          <t>Sunday Proptech (OYO) has raised ₹200 Crore in funding</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -617,19 +617,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VerbaFlo</t>
+          <t>OfficeBanao</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sayantan Biswas</t>
+          <t>Aman Agarwal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -639,40 +639,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/sayantan-biswas-</t>
+          <t>https://in.linkedin.com/in/amanagarwal23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.verbaflo.ai/</t>
+          <t>https://officebanao.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>sayantan@verbaflo.ai</t>
+          <t>aman.agarwal@officebanao.com</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Congratulations on VerbaFlo's $7M Funding</t>
+          <t>Congrats on the Funding</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hi Sayantan, I came across the news about VerbaFlo securing $7M in funding to scale your AI platform for real estate operations. This is a significant milestone, and I'm excited to see the impact it will have on the industry. As someone who's been following the proptech space, I'm impressed by VerbaFlo's innovative approach. I'd love to learn more about your plans for growth and explore potential synergies. Would you be open to a quick 15-minute chat? Best regards, Imran</t>
+          <t>Aman, I saw that OfficeBanao just raised $4 million in funding led by Lightspeed VP - that's exciting news. I'd love to learn more about what's next for the company. Can we schedule a 15-minute call to discuss how things are going?</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNTVQ1M1VtbUNjblhKeFZEUTRHT0lJMkZOalZaWWVmOGhvS2dLUWdqemtEcDVFRXZSbXhxQVFvQkhlQkVvdjV1aFQ5Rm5Xbmp3MFpLRmZUWVdTcFNpVmVmYlB6X2pEUmo2UkxfYzJZUnJOd0xXY1RWNHlJR01uWmhqM0lDbWZlTWg0a2dBc1dmb2dkWFN2TkxuNU1waXg4SERfZ1pDeWJSNmI0RHlZa1E4UTNDaXdsa0NpOHVHajB0UGYwUV9VSUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOTXRWZllNSl90YmgxYjVMV0UyRFg0dTg0UmRvUFRkRzRHdnUyRHpUdDhYSkdoUGpuVU9kZExsaWxlTmZjenVJZV83SWs4ZjZJdVJzWi11dVlSWVpkRW1jM2luV1F2MXQtbFM0ZWY4UDdLcUR6VWh2YXhsRi11bFZ1bS0xME5teWxjSTlxZllBcU9FaHZzSHBLVEVwS0hMZ05tWHNRMmw5WDJmMEJTV2ZIVjBXdmZaSk8zdW1fSVgtU2E2MTlYbjJueUN1RjFYNHRfZVA5VjdUa0_SAdgBQVVfeXFMTk10VmZZTUpfdGJoMWI1TFdFMkRYNHU4NFJkb1BUZEc0R3Z1MkR6VHQ4WEpHaFBqblVPZGRMbGlsZU5mY3p1SWVfN0lrOGY2SXVSc1otdXVZUllaZEVtYzNpbldRdjF0LWxTNGVmOFA3S3FEelVodmF4bEYtdWxWdW0tMTBObXlsY0k5cWZZQXFPRWh2c0hwS1RFcEtITGdObVhzUTJsOVgyZjBCU1dmSFYwV3ZmWkpPM3VtX0lYLVNhNjE5WG4ybnlDdUYxWDR0X2VQOVY3VGtP?oc=5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Proptech startup VerbaFlo secures $7M in funding to scale AI platform for real estate operations</t>
+          <t>OfficeBanao raises $4 million in funding led by Lightspeed VP</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -680,7 +680,70 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aurum PropTech</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ashish Deora</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/in/ashish-deora-aurumventures</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://aurumproptech.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ashish.deora@aurumproptech.com</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Congrats on the Recent Asset Sale</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ashish, I saw the news about Aurum PropTech's ₹112 Crore asset sale and the subsequent rise in shares - that's a significant milestone. I'd love to learn more about your company's growth plans and explore potential opportunities. Can we schedule a 15-minute call to discuss further?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBlRmZ3UjB0ZmZNSWl2cm5BYTJzOEJScFZKUVVhR21tV2RhT21jaDRIU29wcmNoUFlSc2VzYTBLZzJrazNZMGg4SlNnSHY4WkhZQ003RDFCR0tWcXBIRmNORXJUZVNTTGpjUy15OElKWkpyM2tzeTZtTUNuS2g?oc=5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Aurum PropTech approves ₹112 Crore asset sale, shares rise 7.53%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
         </is>
       </c>
     </row>
